--- a/analysis/tables/pythia-12b.xlsx
+++ b/analysis/tables/pythia-12b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8869978118948015</v>
+        <v>0.6445517433102225</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.154845309585795</v>
+        <v>-0.06023220965034953</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.887x - 0.155</t>
+          <t>y = 0.645x - 0.060</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8534228964415241</v>
+        <v>0.8534228964415246</v>
       </c>
       <c r="H3" t="n">
         <v>0.07513563475648484</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1745723692993278</v>
+        <v>0.09344821463210254</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7321525023090065</v>
+        <v>0.584319533659873</v>
       </c>
       <c r="K3" t="n">
         <v>0.1664111261872503</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8793740855497587</v>
+        <v>0.6426803832232895</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1296417813025106</v>
+        <v>-0.05450159982667657</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.879x - 0.130</t>
+          <t>y = 0.643x - 0.055</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8584341219557329</v>
+        <v>0.8562413837773374</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07493913472866838</v>
+        <v>0.07502511631377713</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1474250645235496</v>
+        <v>0.08480358394219234</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7497323042472481</v>
+        <v>0.5881787833966129</v>
       </c>
       <c r="K4" t="n">
         <v>0.1664111261872503</v>
